--- a/docs/02. Source Systems/02. Loan Origination System/LOS_Data_Dictionary.xlsx
+++ b/docs/02. Source Systems/02. Loan Origination System/LOS_Data_Dictionary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\consumer-finance-analytics-platform\docs\02. Source Systems\02. LOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\consumer-finance-analytics-platform\docs\02. Source Systems\02. Loan Origination System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E6DE3C-6EA0-43DC-B119-22A3BBBC7525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E542E187-3C8E-4394-8688-54A15EA97DC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="245">
   <si>
     <t>Column</t>
   </si>
@@ -754,6 +754,12 @@
   </si>
   <si>
     <t>Thời điểm tạo bản ghi yêu cầu giải ngân.</t>
+  </si>
+  <si>
+    <t>customer_id</t>
+  </si>
+  <si>
+    <t>Mã khách hàng</t>
   </si>
 </sst>
 </file>
@@ -813,7 +819,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -826,6 +832,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -993,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1113,33 +1122,31 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" ht="27.6">
       <c r="A5" s="2" t="s">
-        <v>23</v>
+        <v>243</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="2" t="s">
-        <v>25</v>
+      <c r="I5" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="41.4">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>24</v>
@@ -1149,23 +1156,21 @@
       <c r="E6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="F6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="27.6">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="41.4">
       <c r="A7" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>24</v>
@@ -1176,21 +1181,25 @@
         <v>12</v>
       </c>
       <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="G7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="I7" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="27.6">
       <c r="A8" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1199,22 +1208,20 @@
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="27.6">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -1224,64 +1231,66 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="27.6">
       <c r="A10" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="27.6">
       <c r="A11" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="I11" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="27.6">
       <c r="A12" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>51</v>
@@ -1292,20 +1301,18 @@
         <v>12</v>
       </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="2" t="s">
-        <v>55</v>
-      </c>
+      <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="27.6">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>51</v>
@@ -1321,9 +1328,33 @@
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="27.6">
+      <c r="A14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>60</v>
       </c>
     </row>
